--- a/client-env/profiling/client_profiling.xlsx
+++ b/client-env/profiling/client_profiling.xlsx
@@ -8,26 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tuSemesters\Semester Winter 2022_23\Bachelor Thesis\sharded-distributed-databases\client-env\profiling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{551C7990-A89A-4A7D-91C6-C9E4616F48A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9DE080-1ACA-4751-B326-FFC2EF0D8BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="16440" windowHeight="29040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="16440" windowHeight="29040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="test_connection" sheetId="1" r:id="rId1"/>
-    <sheet name="set" sheetId="2" r:id="rId2"/>
-    <sheet name="get" sheetId="3" r:id="rId3"/>
-    <sheet name="get_range" sheetId="4" r:id="rId4"/>
-    <sheet name="del_keys" sheetId="5" r:id="rId5"/>
-    <sheet name="del_values" sheetId="6" r:id="rId6"/>
-    <sheet name="2.Profiling" sheetId="7" r:id="rId7"/>
-    <sheet name="3. Profiling" sheetId="8" r:id="rId8"/>
+    <sheet name="set_single" sheetId="9" r:id="rId2"/>
+    <sheet name="set" sheetId="2" r:id="rId3"/>
+    <sheet name="get" sheetId="3" r:id="rId4"/>
+    <sheet name="get_range" sheetId="4" r:id="rId5"/>
+    <sheet name="del_keys" sheetId="5" r:id="rId6"/>
+    <sheet name="del_values" sheetId="6" r:id="rId7"/>
+    <sheet name="2.Profiling" sheetId="7" r:id="rId8"/>
+    <sheet name="3. Profiling" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="30">
   <si>
     <t>Middleware_Server: 10.0.2.87 (zs07)</t>
   </si>
@@ -114,6 +115,9 @@
   </si>
   <si>
     <t>Configs: VIRTUAL_SITES = 5</t>
+  </si>
+  <si>
+    <t>Total_Time [Initial]_[Connection_Setup]</t>
   </si>
 </sst>
 </file>
@@ -347,7 +351,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -379,8 +383,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -388,6 +390,9 @@
     <xf numFmtId="169" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -705,7 +710,7 @@
   <dimension ref="A1:Q84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.42578125" customWidth="1"/>
+    <col min="1" max="1" width="39" customWidth="1"/>
     <col min="2" max="2" width="37.85546875" customWidth="1"/>
     <col min="3" max="3" width="33.5703125" customWidth="1"/>
     <col min="4" max="4" width="23.85546875" customWidth="1"/>
@@ -738,47 +743,47 @@
       <c r="A6" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="27" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="25"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="27">
+      <c r="A7" s="33">
         <v>1</v>
       </c>
-      <c r="B7" s="31">
-        <v>0</v>
-      </c>
-      <c r="C7" s="31">
-        <v>5.1743999356403904E-3</v>
+      <c r="B7" s="29">
+        <v>7.0000533014535904E-7</v>
+      </c>
+      <c r="C7" s="29">
+        <v>6.2809999799355804E-3</v>
       </c>
       <c r="D7" s="21"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="27">
+      <c r="A8" s="33">
         <v>10</v>
       </c>
-      <c r="B8" s="31">
-        <v>0</v>
-      </c>
-      <c r="C8" s="33">
-        <v>8.2283001393079703E-4</v>
+      <c r="B8" s="29">
+        <v>3.2000243663787799E-6</v>
+      </c>
+      <c r="C8" s="31">
+        <v>2.9709199909120701E-2</v>
       </c>
       <c r="D8" s="22"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="27">
+      <c r="A9" s="33">
         <v>100</v>
       </c>
-      <c r="B9" s="31">
-        <v>0</v>
-      </c>
-      <c r="C9" s="31">
-        <v>5.3790500271134003E-4</v>
+      <c r="B9" s="29">
+        <v>2.06999247893691E-5</v>
+      </c>
+      <c r="C9" s="29">
+        <v>0.24735639989375999</v>
       </c>
       <c r="D9" s="21"/>
       <c r="I9" s="20"/>
@@ -786,106 +791,107 @@
       <c r="Q9" s="2"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="27">
+      <c r="A10" s="33">
         <v>1000</v>
       </c>
-      <c r="B10" s="31">
-        <v>0</v>
-      </c>
-      <c r="C10" s="31">
-        <v>3.6490820092149E-4</v>
+      <c r="B10" s="29">
+        <v>5.5799959227442701E-5</v>
+      </c>
+      <c r="C10" s="29">
+        <v>2.4106429001549201</v>
       </c>
       <c r="D10" s="23"/>
       <c r="H10" s="20"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="27">
-        <v>10000</v>
-      </c>
-      <c r="B11" s="31">
-        <v>0</v>
-      </c>
-      <c r="C11" s="31">
-        <v>3.3099438004428498E-4</v>
-      </c>
+      <c r="A11" s="33"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
       <c r="D11" s="21"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="27"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31">
-        <v>0</v>
-      </c>
+      <c r="A12" s="33"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
       <c r="D12" s="23"/>
       <c r="E12" s="17"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="27"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31">
-        <v>0</v>
-      </c>
+      <c r="A13" s="33"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
       <c r="D13" s="21"/>
       <c r="E13" s="17"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="27"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31">
-        <v>0</v>
-      </c>
+      <c r="A14" s="33"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
       <c r="D14" s="21"/>
     </row>
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32">
-        <v>0</v>
-      </c>
+      <c r="A15" s="34"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
       <c r="D15" s="24"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="32"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="32"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="32"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="32" t="s">
+        <v>29</v>
+      </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="32">
+        <v>6.6191999940201597E-3</v>
+      </c>
       <c r="B20" s="4"/>
       <c r="C20" s="3"/>
       <c r="D20" s="17"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="32"/>
       <c r="B21" s="4"/>
       <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="32"/>
       <c r="B22" s="4"/>
       <c r="C22" s="3"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="32"/>
       <c r="B23" s="4"/>
       <c r="C23" s="3"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="32"/>
       <c r="B24" s="5"/>
       <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="32"/>
       <c r="B25" s="4"/>
       <c r="C25" s="3"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="32"/>
       <c r="B26" s="4"/>
       <c r="C26" s="3"/>
     </row>
@@ -901,7 +907,7 @@
       <c r="B28" s="5"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="30">
+      <c r="A29" s="28">
         <v>2.08998244488611E-7</v>
       </c>
     </row>
@@ -1105,11 +1111,420 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{349D7314-AB8E-4AA0-A861-31CE52CA3EE8}">
+  <dimension ref="A1:Q84"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="2" max="2" width="37.85546875" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="25"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="33">
+        <v>1</v>
+      </c>
+      <c r="B7" s="29">
+        <v>0</v>
+      </c>
+      <c r="C7" s="29">
+        <v>0</v>
+      </c>
+      <c r="D7" s="21"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="33">
+        <v>10</v>
+      </c>
+      <c r="B8" s="29">
+        <v>0</v>
+      </c>
+      <c r="C8" s="31">
+        <v>0</v>
+      </c>
+      <c r="D8" s="22"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="33">
+        <v>100</v>
+      </c>
+      <c r="B9" s="29">
+        <v>0</v>
+      </c>
+      <c r="C9" s="29">
+        <v>0</v>
+      </c>
+      <c r="D9" s="21"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="Q9" s="2"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="33">
+        <v>1000</v>
+      </c>
+      <c r="B10" s="29">
+        <v>0</v>
+      </c>
+      <c r="C10" s="29">
+        <v>0</v>
+      </c>
+      <c r="D10" s="23"/>
+      <c r="H10" s="20"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="33"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="21"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="33"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="17"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="33"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="17"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="33"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="21"/>
+    </row>
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="34"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="24"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="32"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="32"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="32"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="32">
+        <v>6.6191999940201597E-3</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="17"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="32"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="32"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="32"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="32"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="32"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="32"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" s="5"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="28">
+        <v>2.08998244488611E-7</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="4"/>
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C34" s="4"/>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="5"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="4"/>
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="4"/>
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="4"/>
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="4"/>
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="4"/>
+      <c r="C40" s="3"/>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="4"/>
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="4"/>
+      <c r="C42" s="3"/>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="4"/>
+      <c r="C43" s="3"/>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="4"/>
+      <c r="C44" s="3"/>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="4"/>
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="4"/>
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="4"/>
+      <c r="C47" s="3"/>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="4"/>
+      <c r="C48" s="3"/>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="4"/>
+      <c r="C49" s="3"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="4"/>
+      <c r="C50" s="3"/>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="4"/>
+      <c r="C51" s="3"/>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="4"/>
+      <c r="C52" s="3"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="4"/>
+      <c r="C53" s="3"/>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="4"/>
+      <c r="C54" s="3"/>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="4"/>
+      <c r="C55" s="3"/>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="4"/>
+      <c r="C56" s="3"/>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="4"/>
+      <c r="C57" s="3"/>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="4"/>
+      <c r="C58" s="3"/>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="4"/>
+      <c r="C59" s="3"/>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="4"/>
+      <c r="C60" s="3"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="4"/>
+      <c r="C61" s="3"/>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="4"/>
+      <c r="C62" s="3"/>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="4"/>
+      <c r="C63" s="3"/>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="4"/>
+      <c r="C64" s="3"/>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="4"/>
+      <c r="C65" s="3"/>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="4"/>
+      <c r="C66" s="3"/>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B67" s="4"/>
+      <c r="C67" s="3"/>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B68" s="4"/>
+      <c r="C68" s="3"/>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B69" s="4"/>
+      <c r="C69" s="3"/>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B70" s="4"/>
+      <c r="C70" s="3"/>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="4"/>
+      <c r="C71" s="3"/>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B72" s="4"/>
+      <c r="C72" s="3"/>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B73" s="4"/>
+      <c r="C73" s="3"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B74" s="4"/>
+      <c r="C74" s="3"/>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B75" s="4"/>
+      <c r="C75" s="3"/>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B76" s="4"/>
+      <c r="C76" s="1"/>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C77" s="1"/>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C78" s="1"/>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C79" s="1"/>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C80" s="1"/>
+    </row>
+    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C81" s="1"/>
+    </row>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C82" s="1"/>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C83" s="1"/>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C84" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1118,7 +1533,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1127,7 +1542,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1136,7 +1551,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1145,7 +1560,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1154,7 +1569,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1351,7 +1766,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/client-env/profiling/client_profiling.xlsx
+++ b/client-env/profiling/client_profiling.xlsx
@@ -8,27 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tuSemesters\Semester Winter 2022_23\Bachelor Thesis\sharded-distributed-databases\client-env\profiling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9DE080-1ACA-4751-B326-FFC2EF0D8BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADF53A2-C557-4C14-B92E-156F50CDD736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="16440" windowHeight="29040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="16440" windowHeight="29040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="test_connection" sheetId="1" r:id="rId1"/>
-    <sheet name="set_single" sheetId="9" r:id="rId2"/>
-    <sheet name="set" sheetId="2" r:id="rId3"/>
-    <sheet name="get" sheetId="3" r:id="rId4"/>
-    <sheet name="get_range" sheetId="4" r:id="rId5"/>
-    <sheet name="del_keys" sheetId="5" r:id="rId6"/>
-    <sheet name="del_values" sheetId="6" r:id="rId7"/>
-    <sheet name="2.Profiling" sheetId="7" r:id="rId8"/>
-    <sheet name="3. Profiling" sheetId="8" r:id="rId9"/>
+    <sheet name="set" sheetId="9" r:id="rId2"/>
+    <sheet name="get" sheetId="3" r:id="rId3"/>
+    <sheet name="get_range" sheetId="4" r:id="rId4"/>
+    <sheet name="del_keys" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="19">
   <si>
     <t>Middleware_Server: 10.0.2.87 (zs07)</t>
   </si>
@@ -63,61 +59,28 @@
     <t>Deviation (Error) Wall Time</t>
   </si>
   <si>
-    <t>Time Unit: Seconds</t>
+    <t>Total_Time [Initial]_[Connection_Setup]</t>
   </si>
   <si>
-    <t>Functions</t>
+    <t>Function</t>
   </si>
   <si>
-    <t>Request Range/Values</t>
+    <t>set_single</t>
   </si>
   <si>
-    <t>Response Range/Values</t>
+    <t>set_multiples</t>
   </si>
   <si>
-    <t>set_multiples(Keys, Mappings)</t>
+    <t>get_all</t>
   </si>
   <si>
-    <t>1000 Key-Value Pairs</t>
+    <t>get_single</t>
   </si>
   <si>
-    <t>String: OK</t>
+    <t>get_range</t>
   </si>
   <si>
-    <t>get_multiples(Keys)</t>
-  </si>
-  <si>
-    <t>1000 Keys</t>
-  </si>
-  <si>
-    <t>get_range(Start, End)</t>
-  </si>
-  <si>
-    <t>Start:0, End:999</t>
-  </si>
-  <si>
-    <t>del_keys(Keys)</t>
-  </si>
-  <si>
-    <t>10000 Key-Value Pairs</t>
-  </si>
-  <si>
-    <t>10000 Keys</t>
-  </si>
-  <si>
-    <t>Start:0, End:9999</t>
-  </si>
-  <si>
-    <t>Client Instances: 1</t>
-  </si>
-  <si>
-    <t>Server: 10.0.2.87 (zs07)</t>
-  </si>
-  <si>
-    <t>Configs: VIRTUAL_SITES = 5</t>
-  </si>
-  <si>
-    <t>Total_Time [Initial]_[Connection_Setup]</t>
+    <t>del_keys</t>
   </si>
 </sst>
 </file>
@@ -132,7 +95,7 @@
     <numFmt numFmtId="168" formatCode="0.0000000000E+00"/>
     <numFmt numFmtId="169" formatCode="0.0000000000000000E+00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,119 +123,27 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="15">
+  <borders count="7">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -351,48 +222,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -740,158 +600,158 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="25"/>
+      <c r="D6" s="12"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="33">
+      <c r="A7" s="20">
         <v>1</v>
       </c>
-      <c r="B7" s="29">
-        <v>7.0000533014535904E-7</v>
-      </c>
-      <c r="C7" s="29">
-        <v>6.2809999799355804E-3</v>
-      </c>
-      <c r="D7" s="21"/>
+      <c r="B7" s="16">
+        <v>6.0000456869602203E-7</v>
+      </c>
+      <c r="C7" s="16">
+        <v>6.53220003005117E-3</v>
+      </c>
+      <c r="D7" s="8"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="33">
+      <c r="A8" s="20">
         <v>10</v>
       </c>
-      <c r="B8" s="29">
-        <v>3.2000243663787799E-6</v>
-      </c>
-      <c r="C8" s="31">
-        <v>2.9709199909120701E-2</v>
-      </c>
-      <c r="D8" s="22"/>
+      <c r="B8" s="16">
+        <v>1.20000913739204E-6</v>
+      </c>
+      <c r="C8" s="18">
+        <v>3.0956399976275799E-2</v>
+      </c>
+      <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="33">
+      <c r="A9" s="20">
         <v>100</v>
       </c>
-      <c r="B9" s="29">
-        <v>2.06999247893691E-5</v>
-      </c>
-      <c r="C9" s="29">
-        <v>0.24735639989375999</v>
-      </c>
-      <c r="D9" s="21"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
+      <c r="B9" s="16">
+        <v>5.99992927163839E-6</v>
+      </c>
+      <c r="C9" s="16">
+        <v>0.275612499914132</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
       <c r="Q9" s="2"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="33">
+      <c r="A10" s="20">
         <v>1000</v>
       </c>
-      <c r="B10" s="29">
-        <v>5.5799959227442701E-5</v>
-      </c>
-      <c r="C10" s="29">
-        <v>2.4106429001549201</v>
-      </c>
-      <c r="D10" s="23"/>
-      <c r="H10" s="20"/>
+      <c r="B10" s="16">
+        <v>5.5500073358416503E-5</v>
+      </c>
+      <c r="C10" s="16">
+        <v>2.43718340049963</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="21"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="8"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="17"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="6"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="33"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="17"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="33"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="21"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="24"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="11"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="32"/>
+      <c r="A16" s="19"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="32"/>
+      <c r="A17" s="19"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="32"/>
+      <c r="A18" s="19"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
-        <v>29</v>
+      <c r="A19" s="19" t="s">
+        <v>11</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="32">
+      <c r="A20" s="19">
         <v>6.6191999940201597E-3</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="3"/>
-      <c r="D20" s="17"/>
+      <c r="D20" s="6"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="32"/>
+      <c r="A21" s="19"/>
       <c r="B21" s="4"/>
       <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="32"/>
+      <c r="A22" s="19"/>
       <c r="B22" s="4"/>
       <c r="C22" s="3"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="32"/>
+      <c r="A23" s="19"/>
       <c r="B23" s="4"/>
       <c r="C23" s="3"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="32"/>
+      <c r="A24" s="19"/>
       <c r="B24" s="5"/>
       <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="32"/>
+      <c r="A25" s="19"/>
       <c r="B25" s="4"/>
       <c r="C25" s="3"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="32"/>
+      <c r="A26" s="19"/>
       <c r="B26" s="4"/>
       <c r="C26" s="3"/>
     </row>
@@ -907,7 +767,7 @@
       <c r="B28" s="5"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="28">
+      <c r="A29" s="15">
         <v>2.08998244488611E-7</v>
       </c>
     </row>
@@ -1150,158 +1010,168 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="25"/>
+      <c r="D6" s="12" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="33">
+      <c r="A7" s="20">
         <v>1</v>
       </c>
-      <c r="B7" s="29">
-        <v>0</v>
-      </c>
-      <c r="C7" s="29">
-        <v>0</v>
-      </c>
-      <c r="D7" s="21"/>
+      <c r="B7" s="16">
+        <v>1.19989272207021E-7</v>
+      </c>
+      <c r="C7" s="18">
+        <v>3.6088000168092499E-3</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="33">
+      <c r="A8" s="20">
         <v>10</v>
       </c>
-      <c r="B8" s="29">
-        <v>0</v>
-      </c>
-      <c r="C8" s="31">
-        <v>0</v>
-      </c>
-      <c r="D8" s="22"/>
+      <c r="B8" s="16">
+        <v>1.6000121831893901E-7</v>
+      </c>
+      <c r="C8" s="18">
+        <v>6.8087500054389198E-3</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="33">
+      <c r="A9" s="20">
         <v>100</v>
       </c>
-      <c r="B9" s="29">
-        <v>0</v>
-      </c>
-      <c r="C9" s="29">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
+      <c r="B9" s="16">
+        <v>2.2000167518854101E-7</v>
+      </c>
+      <c r="C9" s="16">
+        <v>1.04135300032794E-2</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
       <c r="Q9" s="2"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="33">
+      <c r="A10" s="20">
         <v>1000</v>
       </c>
-      <c r="B10" s="29">
-        <v>0</v>
-      </c>
-      <c r="C10" s="29">
-        <v>0</v>
-      </c>
-      <c r="D10" s="23"/>
-      <c r="H10" s="20"/>
+      <c r="B10" s="16">
+        <v>4.9000373110175105E-7</v>
+      </c>
+      <c r="C10" s="16">
+        <v>5.5644339986611099E-2</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="21"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="8"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="17"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="6"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="33"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="17"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="33"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="21"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="24"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="11"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="32"/>
+      <c r="A16" s="19"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="32"/>
+      <c r="A17" s="19"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="32"/>
+      <c r="A18" s="19"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
-        <v>29</v>
+      <c r="A19" s="19" t="s">
+        <v>11</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="32">
+      <c r="A20" s="19">
         <v>6.6191999940201597E-3</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="3"/>
-      <c r="D20" s="17"/>
+      <c r="D20" s="6"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="32"/>
+      <c r="A21" s="19"/>
       <c r="B21" s="4"/>
       <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="32"/>
+      <c r="A22" s="19"/>
       <c r="B22" s="4"/>
       <c r="C22" s="3"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="32"/>
+      <c r="A23" s="19"/>
       <c r="B23" s="4"/>
       <c r="C23" s="3"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="32"/>
+      <c r="A24" s="19"/>
       <c r="B24" s="5"/>
       <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="32"/>
+      <c r="A25" s="19"/>
       <c r="B25" s="4"/>
       <c r="C25" s="3"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="32"/>
+      <c r="A26" s="19"/>
       <c r="B26" s="4"/>
       <c r="C26" s="3"/>
     </row>
@@ -1317,7 +1187,427 @@
       <c r="B28" s="5"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="28">
+      <c r="A29" s="15">
+        <v>2.08998244488611E-7</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="4"/>
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C34" s="4"/>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="5"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="4"/>
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="4"/>
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="4"/>
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="4"/>
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="4"/>
+      <c r="C40" s="3"/>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="4"/>
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="4"/>
+      <c r="C42" s="3"/>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="4"/>
+      <c r="C43" s="3"/>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="4"/>
+      <c r="C44" s="3"/>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="4"/>
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="4"/>
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="4"/>
+      <c r="C47" s="3"/>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="4"/>
+      <c r="C48" s="3"/>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="4"/>
+      <c r="C49" s="3"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="4"/>
+      <c r="C50" s="3"/>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="4"/>
+      <c r="C51" s="3"/>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="4"/>
+      <c r="C52" s="3"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="4"/>
+      <c r="C53" s="3"/>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="4"/>
+      <c r="C54" s="3"/>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="4"/>
+      <c r="C55" s="3"/>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="4"/>
+      <c r="C56" s="3"/>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="4"/>
+      <c r="C57" s="3"/>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="4"/>
+      <c r="C58" s="3"/>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="4"/>
+      <c r="C59" s="3"/>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="4"/>
+      <c r="C60" s="3"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="4"/>
+      <c r="C61" s="3"/>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="4"/>
+      <c r="C62" s="3"/>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="4"/>
+      <c r="C63" s="3"/>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="4"/>
+      <c r="C64" s="3"/>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="4"/>
+      <c r="C65" s="3"/>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="4"/>
+      <c r="C66" s="3"/>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B67" s="4"/>
+      <c r="C67" s="3"/>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B68" s="4"/>
+      <c r="C68" s="3"/>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B69" s="4"/>
+      <c r="C69" s="3"/>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B70" s="4"/>
+      <c r="C70" s="3"/>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="4"/>
+      <c r="C71" s="3"/>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B72" s="4"/>
+      <c r="C72" s="3"/>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B73" s="4"/>
+      <c r="C73" s="3"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B74" s="4"/>
+      <c r="C74" s="3"/>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B75" s="4"/>
+      <c r="C75" s="3"/>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B76" s="4"/>
+      <c r="C76" s="1"/>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C77" s="1"/>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C78" s="1"/>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C79" s="1"/>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C80" s="1"/>
+    </row>
+    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C81" s="1"/>
+    </row>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C82" s="1"/>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C83" s="1"/>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C84" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:Q84"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="2" max="2" width="37.85546875" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="20">
+        <v>1</v>
+      </c>
+      <c r="B7" s="16">
+        <v>1.20000913739204E-7</v>
+      </c>
+      <c r="C7" s="18">
+        <v>3.5609999787993701E-3</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="20">
+        <v>10</v>
+      </c>
+      <c r="B8" s="16">
+        <v>2.7000205591320898E-7</v>
+      </c>
+      <c r="C8" s="18">
+        <v>5.7667300105094903E-3</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="20">
+        <v>100</v>
+      </c>
+      <c r="B9" s="16">
+        <v>3.3000251278281199E-7</v>
+      </c>
+      <c r="C9" s="16">
+        <v>1.1480420012958299E-2</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="Q9" s="2"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
+        <v>1000</v>
+      </c>
+      <c r="B10" s="16">
+        <v>0</v>
+      </c>
+      <c r="C10" s="16">
+        <v>5.13304799911566E-2</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="20"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="20"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="8"/>
+    </row>
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="21"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="11"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="19"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="19"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="19"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
+        <v>6.6191999940201597E-3</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="19"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="19"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="19"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="19"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="19"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="19"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" s="5"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="15">
         <v>2.08998244488611E-7</v>
       </c>
     </row>
@@ -1524,416 +1814,838 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="2" max="2" width="37.85546875" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="20">
+        <v>1</v>
+      </c>
+      <c r="B7" s="16">
+        <v>0</v>
+      </c>
+      <c r="C7" s="18">
+        <v>3.43204998644068E-3</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="20">
+        <v>10</v>
+      </c>
+      <c r="B8" s="16">
+        <v>0</v>
+      </c>
+      <c r="C8" s="18">
+        <v>5.06252999491989E-3</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="20">
+        <v>100</v>
+      </c>
+      <c r="B9" s="16">
+        <v>0</v>
+      </c>
+      <c r="C9" s="16">
+        <v>9.98640999896451E-3</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="Q9" s="2"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
+        <v>1000</v>
+      </c>
+      <c r="B10" s="16">
+        <v>0</v>
+      </c>
+      <c r="C10" s="16">
+        <v>4.8389560007490201E-2</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="20"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="20"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="8"/>
+    </row>
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="21"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="11"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="19"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="19"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="19"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
+        <v>6.6191999940201597E-3</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="19"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="19"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="19"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="19"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="19"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="19"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" s="5"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="15">
+        <v>2.08998244488611E-7</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="4"/>
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C34" s="4"/>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="5"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="4"/>
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="4"/>
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="4"/>
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="4"/>
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="4"/>
+      <c r="C40" s="3"/>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="4"/>
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="4"/>
+      <c r="C42" s="3"/>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="4"/>
+      <c r="C43" s="3"/>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="4"/>
+      <c r="C44" s="3"/>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="4"/>
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="4"/>
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="4"/>
+      <c r="C47" s="3"/>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="4"/>
+      <c r="C48" s="3"/>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="4"/>
+      <c r="C49" s="3"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="4"/>
+      <c r="C50" s="3"/>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="4"/>
+      <c r="C51" s="3"/>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="4"/>
+      <c r="C52" s="3"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="4"/>
+      <c r="C53" s="3"/>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="4"/>
+      <c r="C54" s="3"/>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="4"/>
+      <c r="C55" s="3"/>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="4"/>
+      <c r="C56" s="3"/>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="4"/>
+      <c r="C57" s="3"/>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="4"/>
+      <c r="C58" s="3"/>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="4"/>
+      <c r="C59" s="3"/>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="4"/>
+      <c r="C60" s="3"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="4"/>
+      <c r="C61" s="3"/>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="4"/>
+      <c r="C62" s="3"/>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="4"/>
+      <c r="C63" s="3"/>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="4"/>
+      <c r="C64" s="3"/>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="4"/>
+      <c r="C65" s="3"/>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="4"/>
+      <c r="C66" s="3"/>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B67" s="4"/>
+      <c r="C67" s="3"/>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B68" s="4"/>
+      <c r="C68" s="3"/>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B69" s="4"/>
+      <c r="C69" s="3"/>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B70" s="4"/>
+      <c r="C70" s="3"/>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="4"/>
+      <c r="C71" s="3"/>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B72" s="4"/>
+      <c r="C72" s="3"/>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B73" s="4"/>
+      <c r="C73" s="3"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B74" s="4"/>
+      <c r="C74" s="3"/>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B75" s="4"/>
+      <c r="C75" s="3"/>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B76" s="4"/>
+      <c r="C76" s="1"/>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C77" s="1"/>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C78" s="1"/>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C79" s="1"/>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C80" s="1"/>
+    </row>
+    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C81" s="1"/>
+    </row>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C82" s="1"/>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C83" s="1"/>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C84" s="1"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.140625" customWidth="1"/>
-    <col min="2" max="2" width="34.85546875" customWidth="1"/>
-    <col min="3" max="3" width="28.85546875" customWidth="1"/>
-    <col min="4" max="4" width="25.42578125" customWidth="1"/>
-    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="2" max="2" width="37.85546875" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="20">
+        <v>1</v>
+      </c>
+      <c r="B7" s="16">
+        <v>0</v>
+      </c>
+      <c r="C7" s="18">
+        <v>3.3188699977472402E-3</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="20">
+        <v>10</v>
+      </c>
+      <c r="B8" s="16">
+        <v>0</v>
+      </c>
+      <c r="C8" s="18">
+        <v>6.1808899976313102E-3</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="20">
+        <v>100</v>
+      </c>
+      <c r="B9" s="16">
+        <v>0</v>
+      </c>
+      <c r="C9" s="16">
+        <v>9.4462000066414392E-3</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="Q9" s="2"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
+        <v>1000</v>
+      </c>
+      <c r="B10" s="16">
+        <v>0</v>
+      </c>
+      <c r="C10" s="16">
+        <v>3.7843140005134002E-2</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="20"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="20"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="8"/>
+    </row>
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="21"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="11"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="19"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="19"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="19"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="19" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="4">
-        <v>6.6699794842861497E-7</v>
-      </c>
-      <c r="C7" s="3">
-        <v>0.51838867100013797</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="4">
-        <v>6.4100095187313802E-7</v>
-      </c>
-      <c r="C8" s="3">
-        <v>0.427087743999436</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="4">
-        <v>6.2799881561659202E-7</v>
-      </c>
-      <c r="C9" s="3">
-        <v>0.42318007900030302</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="13">
-        <v>7.6200012699700797E-7</v>
-      </c>
-      <c r="C10" s="14">
-        <v>0.59908431000076201</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="4"/>
-      <c r="C11" s="3"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4">
-        <v>7.9999881563708101E-7</v>
-      </c>
-      <c r="C16" s="3">
-        <v>3.4945197119996001</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="4">
-        <v>6.1999890021979798E-7</v>
-      </c>
-      <c r="C17" s="3">
-        <v>3.0697713679983201</v>
-      </c>
-      <c r="D17" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="4">
-        <v>8.4299972513690496E-7</v>
-      </c>
-      <c r="C18" s="3">
-        <v>3.4697741269992499</v>
-      </c>
-      <c r="D18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="13">
-        <v>8.0600148066878298E-7</v>
-      </c>
-      <c r="C19" s="14">
-        <v>5.7450908680002604</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="27.5703125" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" customWidth="1"/>
-    <col min="3" max="3" width="27.28515625" customWidth="1"/>
-    <col min="4" max="4" width="26.42578125" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" customWidth="1"/>
-    <col min="6" max="6" width="26.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="3">
-        <v>0.47043957799996799</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="3"/>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="3"/>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="3"/>
-      <c r="D15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="3"/>
-      <c r="D16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>17</v>
-      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
+        <v>6.6191999940201597E-3</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="19"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="19"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="19"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="19"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="19"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="19"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" s="5"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="15">
+        <v>2.08998244488611E-7</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="4"/>
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C34" s="4"/>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="5"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="4"/>
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="4"/>
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="4"/>
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="4"/>
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="4"/>
+      <c r="C40" s="3"/>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="4"/>
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="4"/>
+      <c r="C42" s="3"/>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="4"/>
+      <c r="C43" s="3"/>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="4"/>
+      <c r="C44" s="3"/>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="4"/>
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="4"/>
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="4"/>
+      <c r="C47" s="3"/>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="4"/>
+      <c r="C48" s="3"/>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="4"/>
+      <c r="C49" s="3"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="4"/>
+      <c r="C50" s="3"/>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="4"/>
+      <c r="C51" s="3"/>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="4"/>
+      <c r="C52" s="3"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="4"/>
+      <c r="C53" s="3"/>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="4"/>
+      <c r="C54" s="3"/>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="4"/>
+      <c r="C55" s="3"/>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="4"/>
+      <c r="C56" s="3"/>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="4"/>
+      <c r="C57" s="3"/>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="4"/>
+      <c r="C58" s="3"/>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="4"/>
+      <c r="C59" s="3"/>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="4"/>
+      <c r="C60" s="3"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="4"/>
+      <c r="C61" s="3"/>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="4"/>
+      <c r="C62" s="3"/>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="4"/>
+      <c r="C63" s="3"/>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="4"/>
+      <c r="C64" s="3"/>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="4"/>
+      <c r="C65" s="3"/>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="4"/>
+      <c r="C66" s="3"/>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B67" s="4"/>
+      <c r="C67" s="3"/>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B68" s="4"/>
+      <c r="C68" s="3"/>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B69" s="4"/>
+      <c r="C69" s="3"/>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B70" s="4"/>
+      <c r="C70" s="3"/>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="4"/>
+      <c r="C71" s="3"/>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B72" s="4"/>
+      <c r="C72" s="3"/>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B73" s="4"/>
+      <c r="C73" s="3"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B74" s="4"/>
+      <c r="C74" s="3"/>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B75" s="4"/>
+      <c r="C75" s="3"/>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B76" s="4"/>
+      <c r="C76" s="1"/>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C77" s="1"/>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C78" s="1"/>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C79" s="1"/>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C80" s="1"/>
+    </row>
+    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C81" s="1"/>
+    </row>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C82" s="1"/>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C83" s="1"/>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C84" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/client-env/profiling/client_profiling.xlsx
+++ b/client-env/profiling/client_profiling.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tuSemesters\Semester Winter 2022_23\Bachelor Thesis\sharded-distributed-databases\client-env\profiling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADF53A2-C557-4C14-B92E-156F50CDD736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5BF6BA-731C-4430-B362-0140DFF4732B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="16440" windowHeight="29040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="16440" windowHeight="29040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="test_connection" sheetId="1" r:id="rId1"/>
     <sheet name="set" sheetId="9" r:id="rId2"/>
     <sheet name="get" sheetId="3" r:id="rId3"/>
     <sheet name="get_range" sheetId="4" r:id="rId4"/>
-    <sheet name="del_keys" sheetId="5" r:id="rId5"/>
+    <sheet name="delete" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
